--- a/cicada_generator/lib/WHO/antigen/HepA.xlsx
+++ b/cicada_generator/lib/WHO/antigen/HepA.xlsx
@@ -3,9 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="1-dose series" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="2-dose series" sheetId="3" r:id="rId6"/>
+    <sheet state="visible" name="Antigen Series Overview" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Change History" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="FAQ" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="Vaccine Recommendation Category" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="Immunity" sheetId="5" r:id="rId9"/>
+    <sheet state="visible" name="Contraindications" sheetId="6" r:id="rId10"/>
+    <sheet state="visible" name="single-dose series" sheetId="7" r:id="rId11"/>
+    <sheet state="visible" name="2-dose series" sheetId="8" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -13,7 +18,142 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="137">
+  <si>
+    <t xml:space="preserve">Overview</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This workbook holds the immunization supporting data for HepA: the series a patient may be on, the doses in each series, and the evidence of immunity and contraindications that apply. It follows the layout of the CDC CDSi Antigen Supporting Data workbooks (version 4.65), so that one parser reads every workbook.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n/a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Publication Date: n/a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change #</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reason for Change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Question</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Answer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDSi Manifestation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">If the Best Patient Series for the patient is…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AND the patient's current age is on or after the Begin Age and before the End Age…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AND the Target Dose being forecasted is…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AND the patient's risk factor is one of the Included Indications (and not one of the Excluded Indications)…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THEN the Vaccine Recommendation Category is…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vaccine Recommendation Category Specific Material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excel Worksheet Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Best Patient Series Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patient Begin Age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patient End Age (less than)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast Target Dose Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included Indication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excluded Indication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vaccine Recommendation Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Additional Material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinical History Immunity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immunity Guideline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Birth Date Immunity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immunity Birth Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immunity Country of Birth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immunity Exclusion Condition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antigen Contraindication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contraindication (Code)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Text Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Administrative Guidance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contraindication Begin Age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contraindication End Age (less than)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vaccine Contraindication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vaccine Type (CVX)</t>
+  </si>
   <si>
     <t xml:space="preserve">Series Name</t>
   </si>
@@ -30,21 +170,57 @@
     <t xml:space="preserve">Vaccine Group</t>
   </si>
   <si>
+    <t xml:space="preserve">Text</t>
+  </si>
+  <si>
     <t xml:space="preserve">Series Type</t>
   </si>
   <si>
+    <t xml:space="preserve">Type</t>
+  </si>
+  <si>
     <t xml:space="preserve">Risk</t>
   </si>
   <si>
     <t xml:space="preserve">Equivalent Series Groups</t>
   </si>
   <si>
-    <t xml:space="preserve">n/a</t>
+    <t xml:space="preserve">Series Groups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gender</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required Gender</t>
   </si>
   <si>
     <t xml:space="preserve">Select Patient Series</t>
   </si>
   <si>
+    <t xml:space="preserve">Default Series</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product Path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Series Group Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Series Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Series Priority</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Series Preference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum Age To Start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maximum Age To Start</t>
+  </si>
+  <si>
     <t xml:space="preserve">No</t>
   </si>
   <si>
@@ -60,6 +236,15 @@
     <t xml:space="preserve">Indication</t>
   </si>
   <si>
+    <t xml:space="preserve">Observation (Code)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indication Begin Age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indication End Age (less than)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lives in HepA intermediate/high endemicity area (1027)</t>
   </si>
   <si>
@@ -75,12 +260,81 @@
     <t xml:space="preserve">Age</t>
   </si>
   <si>
+    <t xml:space="preserve">Absolute Minimum Age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum Age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earliest Recommended Age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latest Recommended Age (less than)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maximum Age (less than)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effective Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cessation Date</t>
+  </si>
+  <si>
     <t xml:space="preserve">12 months</t>
   </si>
   <si>
+    <t xml:space="preserve">Preferable Interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From Immediate Previous Dose Administered? Y/N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From Target Dose # in Series</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From Most Recent (CVX List)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From Relevant Observation (Code)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Absolute Minimum Interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum Interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earliest Recommended Interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latest Recommended Interval (less than)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interval Priority Flag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allowable Interval</t>
+  </si>
+  <si>
     <t xml:space="preserve">Preferable Vaccine</t>
   </si>
   <si>
+    <t xml:space="preserve">Vaccine Type Begin Age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vaccine Type End Age (less than)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trade Name (MVX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volume (in ml)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast Vaccine Type (Y/N)</t>
+  </si>
+  <si>
     <t xml:space="preserve">HepA, pediatric/adolescent (83)</t>
   </si>
   <si>
@@ -102,9 +356,66 @@
     <t xml:space="preserve">18 years</t>
   </si>
   <si>
+    <t xml:space="preserve">Inadvertent Vaccine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conditional Skip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skip Context</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set Logic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condition Logic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condition ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Begin Age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End Age (less than)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dose Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dose Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dose Count Logic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vaccine Types (CVX List)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Recurring Dose</t>
   </si>
   <si>
+    <t xml:space="preserve">Recurring Dose (Yes/No)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seasonal Recommendation</t>
+  </si>
+  <si>
     <t xml:space="preserve">WHO HepA 2-dose series</t>
   </si>
   <si>
@@ -115,9 +426,6 @@
   </si>
   <si>
     <t xml:space="preserve">18 months</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preferable Interval</t>
   </si>
   <si>
     <t xml:space="preserve">6 months</t>
@@ -361,13 +669,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr defaultRowHeight="15.75" defaultColWidth="14.43"/>
-  <sheetData/>
-  <drawing r:id="rId1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -377,189 +691,33 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -573,15 +731,108 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>22</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -589,303 +840,1883 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3</v>
+        <v>34</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>8</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>61</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8</v>
+        <v>68</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>10</v>
+        <v>72</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>32</v>
+        <v>75</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>8</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>8</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>22</v>
+        <v>87</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>8</v>
+        <v>87</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>23</v>
+        <v>3</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>8</v>
+        <v>91</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>8</v>
+        <v>93</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q31" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="R31" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="S31" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="T31" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="T32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q31" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="R31" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="S31" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="T31" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="T32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="M52" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="N52" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="O52" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="P52" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q52" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="R52" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="S52" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="T52" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N53" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O53" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P53" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q53" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R53" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S53" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="T53" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
